--- a/Document/기획문서_슈팅.xlsx
+++ b/Document/기획문서_슈팅.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git_fork\ProjectShoot\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D2FCDA-724E-448E-BB25-E9AE1C106932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C206714-406E-4C56-B4FD-51743A9E941D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="711" firstSheet="1" activeTab="1" xr2:uid="{F9E8F865-F741-4425-897D-555A2E4B3EBE}"/>
   </bookViews>
   <sheets>
     <sheet name="깃포크 공부" sheetId="11" state="hidden" r:id="rId1"/>
-    <sheet name="player" sheetId="3" r:id="rId2"/>
-    <sheet name="enemy" sheetId="6" r:id="rId3"/>
-    <sheet name="적 일람" sheetId="17" r:id="rId4"/>
-    <sheet name="적 그룹 일람" sheetId="18" r:id="rId5"/>
-    <sheet name="스폰 데이터" sheetId="19" r:id="rId6"/>
+    <sheet name="History" sheetId="21" r:id="rId2"/>
+    <sheet name="player" sheetId="3" r:id="rId3"/>
+    <sheet name="enemy" sheetId="6" r:id="rId4"/>
+    <sheet name="적 일람" sheetId="17" r:id="rId5"/>
+    <sheet name="적 그룹 일람" sheetId="18" r:id="rId6"/>
     <sheet name="생애주기" sheetId="13" r:id="rId7"/>
     <sheet name="카메라 " sheetId="15" r:id="rId8"/>
     <sheet name="개발요청" sheetId="12" r:id="rId9"/>
@@ -43,15 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="359">
-  <si>
-    <t xml:space="preserve">더 좋은 아이디어가 있다면 적극 환영합니다. </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">이 문서에서는 플레이어 기체를 ufc 로 표기합니다 (임시조치)  </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="358">
   <si>
     <t>설명</t>
   </si>
@@ -1393,58 +1385,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>타입</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>시간</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>주기형</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>초</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>장소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>고정형</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">모든 적들은 3초 뒤부터 생성 가능 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>수치1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이름 (노출x)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>몇초에 생성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>몇초마다 생성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>고정영역 생성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>영역순서대로 생성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>컨셉</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1490,6 +1430,66 @@
   </si>
   <si>
     <t>적들끼리 겹침 가능 ( 겹치면서 나오는 상황은 기획의 죄입니다 )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>히스토리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>번호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>날짜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유형</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">페이지 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작성자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이현경</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 히스토리 시트 생성 (커밋로그 쓸때 참조용)
+- 스폰 데이터 시트 삭제 (정책문서에서 스폰 규칙 설정)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>페이지 편집</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">히스토리
+스폰 데이터 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내용 편집</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>생애주기
+플레이어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 생성영역 이미지 최신화(2026-06-12)
+- 이전 설정 반영한 텍스트(고양이,우주선) 내용 삭제</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1497,7 +1497,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1640,6 +1640,15 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -1709,7 +1718,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -1998,6 +2007,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -2007,7 +2027,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2182,6 +2202,12 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2191,11 +2217,47 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6537,330 +6599,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>695325</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>3276600</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="8" name="그룹 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45C01036-CE74-A31A-7636-15FA62E1DDDA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="981075" y="2943225"/>
-          <a:ext cx="3248025" cy="3686175"/>
-          <a:chOff x="1485900" y="2733675"/>
-          <a:chExt cx="3248025" cy="3686175"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="3" name="직사각형 2">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91990DD5-255A-F750-3B6E-1850BDD17738}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="1485900" y="2733675"/>
-            <a:ext cx="3248025" cy="3686175"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="C00000"/>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
-              <a:t>적 제거 영역</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="6" name="직사각형 5">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F8E8040-6664-4BB7-B0CE-F481BF3DD041}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="1895475" y="5120298"/>
-            <a:ext cx="2505075" cy="979854"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:schemeClr val="accent6"/>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="b"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
-              <a:lnSpc>
-                <a:spcPct val="100000"/>
-              </a:lnSpc>
-              <a:spcBef>
-                <a:spcPts val="0"/>
-              </a:spcBef>
-              <a:spcAft>
-                <a:spcPts val="0"/>
-              </a:spcAft>
-              <a:buClrTx/>
-              <a:buSzTx/>
-              <a:buFontTx/>
-              <a:buNone/>
-              <a:tabLst/>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="ko-KR" altLang="ko-KR" sz="1100">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-                <a:effectLst/>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:rPr>
-              <a:t>적 </a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="ko-KR" altLang="en-US" sz="1100">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-                <a:effectLst/>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:rPr>
-              <a:t>생성</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="ko-KR" altLang="ko-KR" sz="1100">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-                <a:effectLst/>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:rPr>
-              <a:t> 영역 </a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ko-KR" sz="1100">
-                <a:solidFill>
-                  <a:schemeClr val="lt1"/>
-                </a:solidFill>
-                <a:effectLst/>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:rPr>
-              <a:t>2</a:t>
-            </a:r>
-            <a:endParaRPr lang="ko-KR" altLang="ko-KR">
-              <a:effectLst/>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="2" name="직사각형 1">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1375B5DC-7507-87D2-5D6B-4B9EEF4481D7}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="1895475" y="3064730"/>
-            <a:ext cx="2509838" cy="2300166"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="92D050"/>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
-              <a:t>적 생성 영역 </a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" altLang="ko-KR" sz="1100"/>
-              <a:t>1</a:t>
-            </a:r>
-            <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="4" name="직사각형 3">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D75DFBBB-8FB3-49AD-99E1-8FC6B8D935BC}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="2373908" y="3429000"/>
-            <a:ext cx="1575762" cy="2343150"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:schemeClr val="accent5">
-              <a:lumMod val="20000"/>
-              <a:lumOff val="80000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr lang="ko-KR" altLang="en-US" sz="1600">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>게임 화면</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>828675</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1752600</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1619250</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>167409</xdr:rowOff>
+      <xdr:rowOff>62634</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -6877,7 +6625,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="5076825" y="4467225"/>
+          <a:off x="7305675" y="4362450"/>
           <a:ext cx="923925" cy="1129434"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -6906,16 +6654,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>495300</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>361950</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>167409</xdr:rowOff>
+      <xdr:rowOff>62634</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1162050</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1028700</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -6930,7 +6678,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4743450" y="5596659"/>
+          <a:off x="6972300" y="5491884"/>
           <a:ext cx="666750" cy="385041"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6962,126 +6710,6 @@
             <a:rPr lang="ko-KR" altLang="en-US" sz="1100"/>
             <a:t>기준점 </a:t>
           </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1657350</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1790700</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="17" name="직사각형 16">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2AF6F334-5958-1357-A1C9-39E595D98243}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2609850" y="5695950"/>
-          <a:ext cx="133350" cy="152400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1647825</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1847850</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="18" name="웃는 얼굴 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B87BC7BC-009D-9B91-401E-88B9EB7CCCD1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2600325" y="3333750"/>
-          <a:ext cx="200025" cy="180975"/>
-        </a:xfrm>
-        <a:prstGeom prst="smileyFace">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -7339,6 +6967,50 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>106600</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>435926</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="그림 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{810205F9-2001-0B8B-DF4C-081FAD8670D9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1059100" y="2924174"/>
+          <a:ext cx="4148851" cy="3743325"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -9169,7 +8841,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="38.25" x14ac:dyDescent="0.3">
       <c r="A1" s="25" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
@@ -9177,26 +8849,26 @@
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="O3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="P3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="H4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="P4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="P5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -9204,7 +8876,7 @@
         <v>2</v>
       </c>
       <c r="G28" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -9221,66 +8893,66 @@
   <sheetData>
     <row r="2" spans="11:11" x14ac:dyDescent="0.3">
       <c r="K2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.3">
       <c r="K25" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.3">
       <c r="K27" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.3">
       <c r="K28" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.3">
       <c r="K30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.3">
       <c r="K32" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34" spans="3:17" x14ac:dyDescent="0.3">
       <c r="K34" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C42" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H42" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C43" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H43" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44" spans="3:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C44" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H44" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="45" spans="3:17" x14ac:dyDescent="0.3">
@@ -9289,7 +8961,7 @@
       <c r="N45" s="2"/>
       <c r="O45" s="3"/>
       <c r="Q45" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="46" spans="3:17" x14ac:dyDescent="0.3">
@@ -9299,22 +8971,22 @@
       <c r="L46" s="4"/>
       <c r="O46" s="5"/>
       <c r="Q46" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="47" spans="3:17" x14ac:dyDescent="0.3">
       <c r="L47" s="4"/>
       <c r="O47" s="5"/>
       <c r="Q47" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="48" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C48" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D48" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L48" s="4"/>
       <c r="O48" s="5"/>
@@ -9323,7 +8995,7 @@
       <c r="L49" s="4"/>
       <c r="O49" s="5"/>
       <c r="Q49" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="50" spans="12:17" x14ac:dyDescent="0.3">
@@ -9334,7 +9006,7 @@
       <c r="L51" s="4"/>
       <c r="O51" s="5"/>
       <c r="Q51" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="52" spans="12:17" x14ac:dyDescent="0.3">
@@ -9400,11 +9072,276 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28EF8635-FE74-4887-8676-BDAB1BB26428}">
+  <dimension ref="A1:R11"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="33.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="63" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" s="31" t="s">
+        <v>345</v>
+      </c>
+      <c r="B3" s="67" t="s">
+        <v>346</v>
+      </c>
+      <c r="C3" s="68"/>
+      <c r="D3" s="22" t="s">
+        <v>350</v>
+      </c>
+      <c r="E3" s="66" t="s">
+        <v>347</v>
+      </c>
+      <c r="F3" s="66"/>
+      <c r="G3" s="67" t="s">
+        <v>348</v>
+      </c>
+      <c r="H3" s="68"/>
+      <c r="I3" s="66" t="s">
+        <v>349</v>
+      </c>
+      <c r="J3" s="66"/>
+      <c r="K3" s="66"/>
+      <c r="L3" s="66"/>
+      <c r="M3" s="66"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="68"/>
+    </row>
+    <row r="4" spans="1:18" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="69">
+        <f>ROW()-ROW($A$3)</f>
+        <v>1</v>
+      </c>
+      <c r="B4" s="70">
+        <v>46185</v>
+      </c>
+      <c r="C4" s="71"/>
+      <c r="D4" s="69" t="s">
+        <v>351</v>
+      </c>
+      <c r="E4" s="72" t="s">
+        <v>353</v>
+      </c>
+      <c r="F4" s="71"/>
+      <c r="G4" s="76" t="s">
+        <v>354</v>
+      </c>
+      <c r="H4" s="65"/>
+      <c r="I4" s="73" t="s">
+        <v>352</v>
+      </c>
+      <c r="J4" s="74"/>
+      <c r="K4" s="74"/>
+      <c r="L4" s="74"/>
+      <c r="M4" s="74"/>
+      <c r="N4" s="74"/>
+      <c r="O4" s="74"/>
+      <c r="P4" s="74"/>
+      <c r="Q4" s="74"/>
+      <c r="R4" s="75"/>
+    </row>
+    <row r="5" spans="1:18" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="69">
+        <f>ROW()-ROW($A$3)</f>
+        <v>2</v>
+      </c>
+      <c r="B5" s="70">
+        <v>46185</v>
+      </c>
+      <c r="C5" s="71"/>
+      <c r="D5" s="69" t="s">
+        <v>351</v>
+      </c>
+      <c r="E5" s="72" t="s">
+        <v>355</v>
+      </c>
+      <c r="F5" s="71"/>
+      <c r="G5" s="76" t="s">
+        <v>356</v>
+      </c>
+      <c r="H5" s="65"/>
+      <c r="I5" s="73" t="s">
+        <v>357</v>
+      </c>
+      <c r="J5" s="74"/>
+      <c r="K5" s="74"/>
+      <c r="L5" s="74"/>
+      <c r="M5" s="74"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="75"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A6" s="69">
+        <f>ROW()-ROW($A$3)</f>
+        <v>3</v>
+      </c>
+      <c r="B6" s="70"/>
+      <c r="C6" s="71"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="72"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="74"/>
+      <c r="K6" s="74"/>
+      <c r="L6" s="74"/>
+      <c r="M6" s="74"/>
+      <c r="N6" s="74"/>
+      <c r="O6" s="74"/>
+      <c r="P6" s="74"/>
+      <c r="Q6" s="74"/>
+      <c r="R6" s="75"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A7" s="69">
+        <f>ROW()-ROW($A$3)</f>
+        <v>4</v>
+      </c>
+      <c r="B7" s="70"/>
+      <c r="C7" s="71"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="72"/>
+      <c r="F7" s="71"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="65"/>
+      <c r="I7" s="73"/>
+      <c r="J7" s="74"/>
+      <c r="K7" s="74"/>
+      <c r="L7" s="74"/>
+      <c r="M7" s="74"/>
+      <c r="N7" s="74"/>
+      <c r="O7" s="74"/>
+      <c r="P7" s="74"/>
+      <c r="Q7" s="74"/>
+      <c r="R7" s="75"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A8" s="69">
+        <f>ROW()-ROW($A$3)</f>
+        <v>5</v>
+      </c>
+      <c r="B8" s="70"/>
+      <c r="C8" s="71"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="72"/>
+      <c r="F8" s="71"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="65"/>
+      <c r="I8" s="73"/>
+      <c r="J8" s="74"/>
+      <c r="K8" s="74"/>
+      <c r="L8" s="74"/>
+      <c r="M8" s="74"/>
+      <c r="N8" s="74"/>
+      <c r="O8" s="74"/>
+      <c r="P8" s="74"/>
+      <c r="Q8" s="74"/>
+      <c r="R8" s="75"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A9" s="69">
+        <f>ROW()-ROW($A$3)</f>
+        <v>6</v>
+      </c>
+      <c r="B9" s="70"/>
+      <c r="C9" s="71"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="72"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="64"/>
+      <c r="H9" s="65"/>
+      <c r="I9" s="73"/>
+      <c r="J9" s="74"/>
+      <c r="K9" s="74"/>
+      <c r="L9" s="74"/>
+      <c r="M9" s="74"/>
+      <c r="N9" s="74"/>
+      <c r="O9" s="74"/>
+      <c r="P9" s="74"/>
+      <c r="Q9" s="74"/>
+      <c r="R9" s="75"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A10" s="69">
+        <f>ROW()-ROW($A$3)</f>
+        <v>7</v>
+      </c>
+      <c r="B10" s="70"/>
+      <c r="C10" s="71"/>
+      <c r="D10" s="69"/>
+      <c r="E10" s="72"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="64"/>
+      <c r="H10" s="65"/>
+      <c r="I10" s="73"/>
+      <c r="J10" s="74"/>
+      <c r="K10" s="74"/>
+      <c r="L10" s="74"/>
+      <c r="M10" s="74"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="74"/>
+      <c r="P10" s="74"/>
+      <c r="Q10" s="74"/>
+      <c r="R10" s="75"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A11" s="69">
+        <f>ROW()-ROW($A$3)</f>
+        <v>8</v>
+      </c>
+      <c r="B11" s="70"/>
+      <c r="C11" s="71"/>
+      <c r="D11" s="69"/>
+      <c r="E11" s="72"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="64"/>
+      <c r="H11" s="65"/>
+      <c r="I11" s="73"/>
+      <c r="J11" s="74"/>
+      <c r="K11" s="74"/>
+      <c r="L11" s="74"/>
+      <c r="M11" s="74"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="74"/>
+      <c r="P11" s="74"/>
+      <c r="Q11" s="74"/>
+      <c r="R11" s="75"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="I10:R10"/>
+    <mergeCell ref="I11:R11"/>
+    <mergeCell ref="I4:R4"/>
+    <mergeCell ref="I5:R5"/>
+    <mergeCell ref="I6:R6"/>
+    <mergeCell ref="I7:R7"/>
+    <mergeCell ref="I8:R8"/>
+    <mergeCell ref="I9:R9"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53EED6F7-E2A1-46EB-98A7-F79E280C4A2A}">
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.25" customWidth="1"/>
@@ -9418,385 +9355,405 @@
   <sheetData>
     <row r="1" spans="1:8" ht="26.25" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="26.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B4" s="9" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B5" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="26.25" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
-        <v>0</v>
-      </c>
+      <c r="H5" s="12"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B6" s="9" t="s">
-        <v>234</v>
+      <c r="B6" s="12">
+        <f t="shared" ref="B6:B13" si="0">ROW()-ROW($B$5)</f>
+        <v>1</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B7" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="11" t="s">
+      <c r="B7" s="12">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="E7" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="H7" s="12"/>
+      <c r="C7" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B8" s="12">
-        <f t="shared" ref="B8:B15" si="0">ROW()-ROW($B$7)</f>
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8">
         <v>1</v>
       </c>
-      <c r="C8" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>32</v>
-      </c>
       <c r="G8" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B9" s="12">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G9" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B10" s="12">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="C10" t="s">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
+        <v>20</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>41</v>
       </c>
       <c r="G10" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B11" s="12">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>13</v>
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="G11" t="s">
-        <v>23</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="E11" s="14"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B12" s="12">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="C12" s="23" t="s">
-        <v>21</v>
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
+        <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G12" t="s">
-        <v>23</v>
+        <v>45</v>
+      </c>
+      <c r="H12" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B13" s="12">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="C13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="14"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B14" s="12"/>
+      <c r="E14" s="14"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B15" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="14"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B14" s="12">
-        <f t="shared" si="0"/>
+      <c r="E15" s="14"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B16" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="G14" t="s">
-        <v>47</v>
-      </c>
-      <c r="H14" t="s">
+      <c r="C16" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E16" s="14"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B17" s="12">
+        <f>ROW()-ROW($B$16)</f>
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B18" s="12">
+        <f>ROW()-ROW($B$16)</f>
+        <v>2</v>
+      </c>
+      <c r="C18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E18" s="14"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="E19" s="14"/>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B20" s="9" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B15" s="12">
-        <f t="shared" si="0"/>
+      <c r="E20" s="14"/>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B21" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B22" s="12">
+        <f>ROW()-ROW($B$21)</f>
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
         <v>8</v>
       </c>
-      <c r="E15" s="14"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B16" s="12"/>
-      <c r="E16" s="14"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B17" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E17" s="14"/>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B18" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" s="11" t="s">
+      <c r="D22" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G22" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B23" s="12">
+        <f t="shared" ref="B23:B27" si="1">ROW()-ROW($B$21)</f>
         <v>2</v>
       </c>
-      <c r="E18" s="14"/>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B19" s="12">
-        <f>ROW()-ROW($B$18)</f>
-        <v>1</v>
-      </c>
-      <c r="C19" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="C23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" t="s">
+        <v>2</v>
+      </c>
+      <c r="E23" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="E19" s="14" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B20" s="12">
-        <f>ROW()-ROW($B$18)</f>
-        <v>2</v>
-      </c>
-      <c r="C20" t="s">
-        <v>95</v>
-      </c>
-      <c r="E20" s="14"/>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="E21" s="14"/>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B22" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E22" s="14"/>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B23" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11" t="s">
-        <v>3</v>
+      <c r="G23" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="12">
-        <f>ROW()-ROW($B$23)</f>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D24" t="s">
         <v>5</v>
       </c>
-      <c r="E24" s="12" t="s">
-        <v>32</v>
+      <c r="E24" s="14" t="s">
+        <v>41</v>
       </c>
       <c r="G24" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="12">
-        <f t="shared" ref="B25:B29" si="1">ROW()-ROW($B$23)</f>
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D25" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G25" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" s="12">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="D26" t="s">
-        <v>7</v>
-      </c>
-      <c r="E26" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="G26" t="s">
-        <v>23</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="E26" s="14"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="12">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C27" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="D27" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="G27" t="s">
+        <v>45</v>
+      </c>
+      <c r="H27" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B29" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B30" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="H30" s="12"/>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B31" s="12">
+        <f t="shared" ref="B31:B39" si="2">ROW()-ROW($B$30)</f>
+        <v>1</v>
+      </c>
+      <c r="C31" t="s">
         <v>22</v>
       </c>
-      <c r="E27" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="G27" t="s">
+      <c r="D31" t="s">
+        <v>3</v>
+      </c>
+      <c r="G31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B32" s="12">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="C32" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B28" s="12">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="C28" t="s">
-        <v>38</v>
-      </c>
-      <c r="D28" t="s">
-        <v>40</v>
-      </c>
-      <c r="E28" s="14"/>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B29" s="12">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="C29" t="s">
-        <v>44</v>
-      </c>
-      <c r="D29" t="s">
-        <v>45</v>
-      </c>
-      <c r="E29" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="G29" t="s">
-        <v>47</v>
-      </c>
-      <c r="H29" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B31" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B32" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D32" s="11" t="s">
+      <c r="D32" t="s">
         <v>2</v>
       </c>
-      <c r="E32" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="H32" s="12"/>
+      <c r="G32" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B33" s="12">
-        <f t="shared" ref="B33:B41" si="2">ROW()-ROW($B$32)</f>
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>3</v>
       </c>
       <c r="C33" t="s">
         <v>24</v>
@@ -9805,109 +9762,79 @@
         <v>5</v>
       </c>
       <c r="G33" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B34" s="12">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C34" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D34" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="G34" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B35" s="12">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C35" t="s">
+        <v>25</v>
+      </c>
+      <c r="D35" t="s">
         <v>26</v>
-      </c>
-      <c r="D35" t="s">
-        <v>7</v>
-      </c>
-      <c r="G35" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B36" s="12">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C36" t="s">
-        <v>21</v>
-      </c>
-      <c r="D36" t="s">
-        <v>22</v>
-      </c>
-      <c r="G36" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B37" s="12">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C37" t="s">
-        <v>27</v>
-      </c>
-      <c r="D37" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B38" s="12">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C38" t="s">
         <v>29</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G38" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B39" s="12">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C39" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B40" s="12">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="C40" t="s">
-        <v>31</v>
-      </c>
-      <c r="E40" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="G40" t="s">
+        <v>33</v>
+      </c>
+      <c r="D39" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B41" s="12">
-        <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-      <c r="C41" t="s">
-        <v>35</v>
-      </c>
-      <c r="D41" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -9917,7 +9844,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F061614-43B1-4419-882C-4D7535310A1A}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -9935,7 +9862,7 @@
   <sheetData>
     <row r="1" spans="2:21" ht="26.25" x14ac:dyDescent="0.3">
       <c r="D1" s="10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E1" s="13"/>
     </row>
@@ -9943,10 +9870,10 @@
       <c r="D2" s="10"/>
       <c r="E2" s="13"/>
       <c r="K2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="Q2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="2:21" ht="27" thickBot="1" x14ac:dyDescent="0.35">
@@ -9975,7 +9902,7 @@
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="K5" s="4"/>
       <c r="O5" s="5"/>
@@ -9990,16 +9917,16 @@
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B7" s="15" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C7" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="17" t="s">
         <v>52</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>54</v>
       </c>
       <c r="K7" s="4"/>
       <c r="O7" s="5"/>
@@ -10011,10 +9938,10 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K8" s="4"/>
       <c r="O8" s="5"/>
@@ -10026,13 +9953,13 @@
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="K9" s="4"/>
       <c r="O9" s="5"/>
@@ -10053,7 +9980,7 @@
     </row>
     <row r="12" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B12" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E12" s="12"/>
       <c r="K12" s="4"/>
@@ -10063,19 +9990,19 @@
     </row>
     <row r="13" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B13" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="11" t="s">
-        <v>11</v>
-      </c>
       <c r="D13" s="11" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K13" s="4"/>
       <c r="O13" s="5"/>
@@ -10088,13 +10015,13 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F14" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K14" s="4"/>
       <c r="O14" s="5"/>
@@ -10107,13 +10034,13 @@
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K15" s="4"/>
       <c r="O15" s="5"/>
@@ -10126,14 +10053,14 @@
         <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E16" s="14"/>
       <c r="F16" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="K16" s="4"/>
       <c r="O16" s="5"/>
@@ -10146,10 +10073,10 @@
         <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D17" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="K17" s="4"/>
       <c r="O17" s="5"/>
@@ -10162,10 +10089,10 @@
         <v>5</v>
       </c>
       <c r="C18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" t="s">
         <v>38</v>
-      </c>
-      <c r="D18" t="s">
-        <v>40</v>
       </c>
       <c r="K18" s="4"/>
       <c r="O18" s="5"/>
@@ -10178,14 +10105,14 @@
         <v>6</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D19" s="20"/>
       <c r="E19" s="19" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K19" s="4"/>
       <c r="O19" s="5"/>
@@ -10200,7 +10127,7 @@
     </row>
     <row r="21" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B21" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K21" s="4"/>
       <c r="O21" s="5"/>
@@ -10209,19 +10136,19 @@
     </row>
     <row r="22" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B22" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="11" t="s">
-        <v>11</v>
-      </c>
       <c r="D22" s="11" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K22" s="4"/>
       <c r="O22" s="5"/>
@@ -10234,13 +10161,13 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D23" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F23" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K23" s="4"/>
       <c r="O23" s="5"/>
@@ -10253,10 +10180,10 @@
         <v>2</v>
       </c>
       <c r="C24" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F24" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K24" s="4"/>
       <c r="O24" s="5"/>
@@ -10269,7 +10196,7 @@
         <v>3</v>
       </c>
       <c r="C25" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="K25" s="4"/>
       <c r="O25" s="5"/>
@@ -10282,7 +10209,7 @@
         <v>4</v>
       </c>
       <c r="C26" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="K26" s="4"/>
       <c r="O26" s="5"/>
@@ -10295,7 +10222,7 @@
         <v>5</v>
       </c>
       <c r="C27" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K27" s="6"/>
       <c r="L27" s="7"/>
@@ -10310,53 +10237,53 @@
     </row>
     <row r="29" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="30" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="32" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B37" s="15" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F37" s="15" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G37" s="15" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H37" s="15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I37" s="15" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.3">
@@ -10364,7 +10291,7 @@
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D38">
         <v>100</v>
@@ -10375,7 +10302,7 @@
         <v>2</v>
       </c>
       <c r="C39" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.3">
@@ -10383,7 +10310,7 @@
         <v>3</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.3">
@@ -10391,30 +10318,30 @@
         <v>4</v>
       </c>
       <c r="C41" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D41" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C42" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C43" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="45" spans="2:9" ht="26.25" x14ac:dyDescent="0.3">
       <c r="B45" s="43" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B46" s="15" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.3">
@@ -10422,7 +10349,7 @@
         <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.3">
@@ -10430,7 +10357,7 @@
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.3">
@@ -10438,7 +10365,7 @@
         <v>3</v>
       </c>
       <c r="C49" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.3">
@@ -10446,7 +10373,7 @@
         <v>4</v>
       </c>
       <c r="C50" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -10456,7 +10383,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96250C9B-AC9A-4D12-8447-AA0DC8C1E6CA}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -10474,81 +10401,81 @@
   <sheetData>
     <row r="1" spans="1:20" ht="26.25" x14ac:dyDescent="0.3">
       <c r="A1" s="44" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="26.25" x14ac:dyDescent="0.3">
       <c r="A2" s="44"/>
       <c r="S2" s="51" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C3" s="15"/>
       <c r="D3" s="15" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E3" s="15"/>
       <c r="F3" s="15"/>
       <c r="G3" s="15" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="H3" s="15"/>
       <c r="I3" s="15"/>
       <c r="J3" s="15"/>
       <c r="K3" s="15"/>
       <c r="S3" s="15" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="S4" s="12">
         <v>1</v>
       </c>
       <c r="T4" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
@@ -10556,13 +10483,13 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -10586,13 +10513,13 @@
         <v>50</v>
       </c>
       <c r="L5" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="S5" s="12">
         <v>2</v>
       </c>
       <c r="T5" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
@@ -10600,22 +10527,22 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="L6" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="S6" s="12">
         <v>3</v>
       </c>
       <c r="T6" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
@@ -10623,22 +10550,22 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="L7" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="S7" s="12">
         <v>4</v>
       </c>
       <c r="T7" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.3">
@@ -10646,19 +10573,19 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E8">
         <v>4</v>
       </c>
       <c r="L8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
@@ -10666,13 +10593,13 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="S9" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.3">
@@ -10680,108 +10607,108 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="S10" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="S11" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B22" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="N22" s="53"/>
       <c r="O22" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="F23" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="N23" s="52"/>
       <c r="O23" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="S24" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B25" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C25" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F25" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F27" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="S27" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>312</v>
+      </c>
+      <c r="B28" t="s">
         <v>314</v>
-      </c>
-      <c r="B28" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="F29" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="B31" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -10791,7 +10718,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BE7DF70-9984-40C4-B7A6-B1FE51D4706D}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -10801,7 +10728,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="26.25" x14ac:dyDescent="0.3">
       <c r="A1" s="44" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="26.25" x14ac:dyDescent="0.3">
@@ -10809,13 +10736,13 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C3" s="54" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D3" s="54"/>
       <c r="E3" s="54"/>
@@ -10825,28 +10752,28 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" s="15" t="s">
+        <v>323</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>324</v>
+      </c>
+      <c r="D4" s="15" t="s">
         <v>325</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="E4" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="F4" s="15" t="s">
         <v>327</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="G4" s="15" t="s">
+        <v>329</v>
+      </c>
+      <c r="H4" s="15" t="s">
         <v>328</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>329</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>331</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -10854,16 +10781,16 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D5" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E5" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -10887,154 +10814,6 @@
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="C10" s="12"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDAE2447-2B8C-4A52-B029-19667817279D}">
-  <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="18.125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="26.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="44" t="s">
-        <v>318</v>
-      </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-    </row>
-    <row r="2" spans="1:9" ht="26.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="44" t="s">
-        <v>340</v>
-      </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-    </row>
-    <row r="3" spans="1:9" ht="26.25" x14ac:dyDescent="0.3">
-      <c r="A3" s="44"/>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
-        <v>269</v>
-      </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15" t="s">
-        <v>270</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>270</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>342</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>334</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>341</v>
-      </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="12">
-        <f>ROW()-ROW($A$5)</f>
-        <v>1</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>344</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>336</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>335</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>337</v>
-      </c>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="12">
-        <f t="shared" ref="A7:A9" si="0">ROW()-ROW($A$5)</f>
-        <v>2</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>343</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>339</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>335</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>337</v>
-      </c>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="12">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>336</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="12">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>345</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>339</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>338</v>
-      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -11048,7 +10827,7 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.125" style="12" customWidth="1"/>
     <col min="3" max="3" width="24.125" style="12" customWidth="1"/>
     <col min="4" max="4" width="29.875" style="12" customWidth="1"/>
     <col min="5" max="5" width="56.5" style="12" bestFit="1" customWidth="1"/>
@@ -11063,410 +10842,410 @@
   <sheetData>
     <row r="1" spans="1:12" ht="31.5" x14ac:dyDescent="0.3">
       <c r="A1" s="35" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="36" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B3" s="37"/>
       <c r="C3" s="37"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B5" s="61" t="s">
-        <v>152</v>
-      </c>
-      <c r="C5" s="61"/>
+      <c r="B5" s="59" t="s">
+        <v>150</v>
+      </c>
+      <c r="C5" s="59"/>
       <c r="D5" s="56"/>
       <c r="E5" s="56" t="s">
-        <v>149</v>
-      </c>
-      <c r="F5" s="62"/>
+        <v>147</v>
+      </c>
+      <c r="F5" s="58"/>
       <c r="G5" s="57"/>
       <c r="H5" s="56" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I5" s="57"/>
       <c r="J5" s="56" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="K5" s="57"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B6" s="29" t="s">
+        <v>149</v>
+      </c>
+      <c r="C6" s="30" t="s">
         <v>151</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="D6" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="E6" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="F6" s="34" t="s">
         <v>153</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="G6" s="28" t="s">
         <v>154</v>
       </c>
-      <c r="E6" s="33" t="s">
-        <v>171</v>
-      </c>
-      <c r="F6" s="34" t="s">
-        <v>155</v>
-      </c>
-      <c r="G6" s="28" t="s">
-        <v>156</v>
-      </c>
       <c r="H6" s="22" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J6" s="29" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="K6" s="28" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="22" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C7" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="D7" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="D7" s="12" t="s">
-        <v>167</v>
-      </c>
       <c r="E7" s="12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B9" s="56" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C9" s="57"/>
       <c r="D9" s="56" t="s">
-        <v>176</v>
-      </c>
-      <c r="E9" s="62"/>
+        <v>174</v>
+      </c>
+      <c r="E9" s="58"/>
       <c r="F9" s="57"/>
       <c r="G9" s="56" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H9" s="57"/>
       <c r="I9" s="56" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J9" s="57"/>
       <c r="K9" s="56" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="L9" s="57"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B10" s="29" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C10" s="30" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D10" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="E10" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="E10" s="34" t="s">
-        <v>192</v>
-      </c>
       <c r="F10" s="28" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H10" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="I10" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="J10" s="28" t="s">
         <v>196</v>
       </c>
-      <c r="I10" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="J10" s="28" t="s">
-        <v>198</v>
-      </c>
       <c r="K10" s="22" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="L10" s="22" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="22" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C11" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="L11" s="12" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="60" t="s">
+        <v>176</v>
+      </c>
+      <c r="D14" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="D11" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="J11" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="K11" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="L11" s="12" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="58" t="s">
+      <c r="E14" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="F14" s="59" t="s">
+        <v>186</v>
+      </c>
+      <c r="G14" s="59"/>
+      <c r="H14" s="59"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="61"/>
+      <c r="D15" s="38" t="s">
         <v>178</v>
       </c>
-      <c r="D14" s="31" t="s">
+      <c r="E15" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="61"/>
+      <c r="D16" s="39" t="s">
         <v>179</v>
       </c>
-      <c r="E14" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="F14" s="61" t="s">
-        <v>188</v>
-      </c>
-      <c r="G14" s="61"/>
-      <c r="H14" s="61"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="59"/>
-      <c r="D15" s="38" t="s">
+      <c r="E16" s="14" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="61"/>
+      <c r="D17" s="27" t="s">
         <v>180</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E17" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="F15" s="14" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="59"/>
-      <c r="D16" s="39" t="s">
-        <v>181</v>
-      </c>
-      <c r="E16" s="14" t="s">
+      <c r="F17" s="14" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="61"/>
+      <c r="D18" s="14" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="59"/>
-      <c r="D17" s="27" t="s">
-        <v>182</v>
-      </c>
-      <c r="E17" s="21" t="s">
-        <v>187</v>
-      </c>
-      <c r="F17" s="14" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="59"/>
-      <c r="D18" s="14" t="s">
-        <v>186</v>
-      </c>
-    </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="59"/>
+      <c r="A19" s="61"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="59"/>
+      <c r="A20" s="61"/>
       <c r="E20" s="40" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="61"/>
+      <c r="E21" s="14" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="61"/>
+      <c r="E22" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="59"/>
-      <c r="E21" s="14" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="59"/>
-      <c r="E22" t="s">
-        <v>220</v>
-      </c>
-    </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="59"/>
+      <c r="A23" s="61"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="59"/>
+      <c r="A24" s="61"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="59"/>
+      <c r="A25" s="61"/>
       <c r="E25" s="12" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="59"/>
+      <c r="A26" s="61"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="59"/>
+      <c r="A27" s="61"/>
       <c r="E27" s="14" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="61"/>
+      <c r="E28" s="14" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="61"/>
+      <c r="E29" s="12" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="59"/>
-      <c r="E28" s="14" t="s">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="61"/>
+      <c r="E30" s="14" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="59"/>
-      <c r="E29" s="12" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="59"/>
-      <c r="E30" s="14" t="s">
-        <v>251</v>
-      </c>
-    </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="60"/>
+      <c r="A31" s="62"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B33" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="C33" s="31" t="s">
         <v>174</v>
       </c>
-      <c r="C33" s="31" t="s">
-        <v>176</v>
-      </c>
       <c r="D33" s="56" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E33" s="57"/>
       <c r="F33" s="56" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G33" s="57"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B34" s="30" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C34" s="33" t="s">
+        <v>206</v>
+      </c>
+      <c r="D34" s="22" t="s">
         <v>208</v>
       </c>
-      <c r="D34" s="22" t="s">
-        <v>210</v>
-      </c>
       <c r="E34" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="F34" s="22" t="s">
         <v>213</v>
       </c>
-      <c r="F34" s="22" t="s">
+      <c r="G34" s="22" t="s">
         <v>215</v>
-      </c>
-      <c r="G34" s="22" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="22" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B35" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="C35" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="D35" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="D35" s="12" t="s">
-        <v>211</v>
-      </c>
       <c r="E35" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="F35" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="F35" s="12" t="s">
-        <v>216</v>
-      </c>
       <c r="G35" s="12" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B38" s="22" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C38" s="22" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D38" s="22" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E38" s="22" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="22" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B39" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="C39" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="D39" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="E39" s="14" t="s">
         <v>243</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="E39" s="14" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="33" x14ac:dyDescent="0.3">
       <c r="E40" s="42" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
@@ -11507,6 +11286,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="A14:A31"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="K9:L9"/>
@@ -11515,11 +11299,6 @@
     <mergeCell ref="E5:G5"/>
     <mergeCell ref="J5:K5"/>
     <mergeCell ref="H5:I5"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="A14:A31"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="B9:C9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11539,15 +11318,15 @@
   <sheetData>
     <row r="1" spans="1:25" ht="26.25" x14ac:dyDescent="0.3">
       <c r="A1" s="43" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="N3" s="45" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="O3" s="45"/>
       <c r="P3" s="45"/>
@@ -11561,13 +11340,13 @@
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C4" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="N4" s="46" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="O4" s="45"/>
       <c r="P4" s="45"/>
@@ -11581,21 +11360,21 @@
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C5" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6" spans="1:25" ht="21.75" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C6" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="N6" s="47" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="O6" s="48"/>
       <c r="P6" s="48"/>
@@ -11628,10 +11407,10 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="N8" s="48" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="O8" s="48"/>
       <c r="P8" s="48"/>
@@ -11647,7 +11426,7 @@
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="N9" s="49"/>
       <c r="O9" s="48"/>
@@ -11664,7 +11443,7 @@
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="N10" s="50" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="O10" s="48"/>
       <c r="P10" s="48"/>
@@ -11683,10 +11462,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="N11" s="50" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="O11" s="48"/>
       <c r="P11" s="48"/>
@@ -11702,7 +11481,7 @@
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.3">
@@ -11710,17 +11489,17 @@
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C15" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
@@ -11728,12 +11507,12 @@
         <v>4</v>
       </c>
       <c r="C18" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -11762,14 +11541,14 @@
   <sheetData>
     <row r="2" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B2" s="15" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D2" s="17"/>
       <c r="H2" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="2:19" x14ac:dyDescent="0.3">
@@ -11777,34 +11556,34 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3" t="s">
         <v>106</v>
       </c>
-      <c r="F3" t="s">
-        <v>108</v>
-      </c>
       <c r="H3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.3">
       <c r="E4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F4" t="s">
         <v>107</v>
-      </c>
-      <c r="F4" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.3">
       <c r="E5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.3">
       <c r="E6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="8" spans="2:19" x14ac:dyDescent="0.3">
@@ -11812,13 +11591,13 @@
         <v>2</v>
       </c>
       <c r="C8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E8" s="41" t="s">
+        <v>228</v>
+      </c>
+      <c r="H8" t="s">
         <v>110</v>
-      </c>
-      <c r="E8" s="41" t="s">
-        <v>230</v>
-      </c>
-      <c r="H8" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.3">
@@ -11826,13 +11605,13 @@
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F10" s="41" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.3">
@@ -11840,27 +11619,27 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E12" t="s">
+        <v>114</v>
+      </c>
+      <c r="H12" t="s">
         <v>116</v>
       </c>
-      <c r="H12" t="s">
-        <v>118</v>
-      </c>
       <c r="J12" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="2:19" x14ac:dyDescent="0.3">
       <c r="C13" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E13" s="41" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J13" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.3">
@@ -11868,13 +11647,13 @@
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H15" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="S15" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.3">
@@ -11885,18 +11664,18 @@
         <v>5.25</v>
       </c>
       <c r="C17" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H17" t="s">
+        <v>141</v>
+      </c>
+      <c r="S17" t="s">
         <v>143</v>
-      </c>
-      <c r="S17" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="18" spans="2:19" x14ac:dyDescent="0.3">
       <c r="S18" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" spans="2:19" x14ac:dyDescent="0.3">
@@ -11904,31 +11683,31 @@
         <v>5.5</v>
       </c>
       <c r="C19" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E19" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H19" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="2:19" x14ac:dyDescent="0.3">
       <c r="E20" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="S20" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="22" spans="2:19" x14ac:dyDescent="0.3">
       <c r="D22" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="24" spans="2:19" x14ac:dyDescent="0.3">
       <c r="D24" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26" spans="2:19" x14ac:dyDescent="0.3">
@@ -11936,60 +11715,60 @@
         <v>6</v>
       </c>
       <c r="C26" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" spans="2:19" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
+        <v>119</v>
+      </c>
+      <c r="D27" t="s">
+        <v>120</v>
+      </c>
+      <c r="E27" t="s">
         <v>121</v>
-      </c>
-      <c r="D27" t="s">
-        <v>122</v>
-      </c>
-      <c r="E27" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="29" spans="2:19" x14ac:dyDescent="0.3">
       <c r="C29" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D29" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="30" spans="2:19" x14ac:dyDescent="0.3">
       <c r="D30" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="32" spans="2:19" x14ac:dyDescent="0.3">
       <c r="C32" t="s">
+        <v>124</v>
+      </c>
+      <c r="D32" t="s">
         <v>126</v>
-      </c>
-      <c r="D32" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C34" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D34" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C36" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D36" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D37" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.3">
@@ -11997,7 +11776,7 @@
         <v>7</v>
       </c>
       <c r="C39" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.3">
@@ -12005,10 +11784,10 @@
         <v>8</v>
       </c>
       <c r="C41" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D41" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.3">
@@ -12016,7 +11795,7 @@
         <v>9</v>
       </c>
       <c r="C43" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.3">
@@ -12024,12 +11803,12 @@
         <v>10</v>
       </c>
       <c r="C45" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C47" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
     </row>
   </sheetData>
